--- a/file/table/DAPC_ERA5.xlsx
+++ b/file/table/DAPC_ERA5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B116C189-3918-4B20-9AB1-F94665E3AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADC98CE-F065-4912-8E03-5D64A2B36143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{DE9D926E-A97C-4AAA-9C06-5A815B2AC859}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{DE9D926E-A97C-4AAA-9C06-5A815B2AC859}"/>
   </bookViews>
   <sheets>
     <sheet name="QGIS_Date" sheetId="1" r:id="rId1"/>
@@ -384,9 +384,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -407,6 +404,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16315,62 +16315,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="19">
         <v>666202495</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="20">
         <f>C5/C9</f>
         <v>248.73151695041815</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <f>C6/1000</f>
         <v>0.24873151695041815</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="21">
         <f>C8*24*60*60</f>
         <v>2678400</v>
       </c>
